--- a/results/Int Task Remove ACC -0.1/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC -0.1/Rando_8_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5398335026655555</v>
+        <v>0.546717142889759</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5384008379091085</v>
+        <v>0.5438075777120743</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5408818403558641</v>
+        <v>0.5521077105141992</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5412661674220025</v>
+        <v>0.5510855337009175</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5420086606772528</v>
+        <v>0.5510855337009175</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5421313789731237</v>
+        <v>0.5547637530108791</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5410307195287618</v>
+        <v>0.5506750457577522</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5410307195287618</v>
+        <v>0.5499506272902659</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5442722900185314</v>
+        <v>0.5499506272902659</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5471637804084521</v>
+        <v>0.5492162201242784</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5463689653991484</v>
+        <v>0.5542043858948161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5446304562076432</v>
+        <v>0.5575767607697196</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5459323165789564</v>
+        <v>0.5575767607697196</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5450409441508084</v>
+        <v>0.5653256125450443</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5517414582358247</v>
+        <v>0.5628969318523422</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5513832920467129</v>
+        <v>0.5654040951761246</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.558101880919493</v>
+        <v>0.5662331571517178</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5592810229949352</v>
+        <v>0.5585447132197096</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5663397032690631</v>
+        <v>0.561007640878701</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5744305490549739</v>
+        <v>0.5602128258693972</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5720361153285616</v>
+        <v>0.5760525234306327</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5849481729243484</v>
+        <v>0.5778956761302451</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5882501512574344</v>
+        <v>0.5676658219081648</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5892461671936894</v>
+        <v>0.5685310334592861</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5816262171942602</v>
+        <v>0.5664424441679319</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5809098848160368</v>
+        <v>0.5730906364988946</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.481672640859675</v>
+        <v>0.5730906364988946</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5171006518339251</v>
+        <v>0.5728109529408631</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4906710312522593</v>
+        <v>0.5763926148319806</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4799341316681697</v>
+        <v>0.5468940855489218</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4147164921973995</v>
+        <v>0.5443426865603489</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4128110290452326</v>
+        <v>0.5468840968504207</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4128110290452326</v>
+        <v>0.5438879629523929</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4266406199461942</v>
+        <v>0.5547214199553268</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4224291943971963</v>
+        <v>0.5654944691149442</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4363957731633161</v>
+        <v>0.5714182429784206</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4422572365742379</v>
+        <v>0.5740823715643634</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4460662602693334</v>
+        <v>0.5805878682024528</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4460662602693334</v>
+        <v>0.5803424316107109</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4217575733360731</v>
+        <v>0.5817127859146033</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.395239481424826</v>
+        <v>0.580447075118818</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3981490466025107</v>
+        <v>0.593123684821364</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.412610303770591</v>
+        <v>0.5825237731024326</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4155541159145653</v>
+        <v>0.5786966746195733</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4156849202996991</v>
+        <v>0.5748614900474511</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4423238278975787</v>
+        <v>0.5790890877749746</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4555716960239272</v>
+        <v>0.5750950353314536</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4577891870911768</v>
+        <v>0.5178293511721975</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4598597015947671</v>
+        <v>0.5158373192996876</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4429374193769335</v>
+        <v>0.5158373192996876</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4555279360114461</v>
+        <v>0.5262864492364829</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4547754540576947</v>
+        <v>0.4831942525980129</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4690374129080621</v>
+        <v>0.4867416675228408</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4638704018691233</v>
+        <v>0.4851601235934961</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4638704018691233</v>
+        <v>0.4827052820237674</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5120658721370488</v>
+        <v>0.4851601235934961</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5014921212951441</v>
+        <v>0.4906634208153061</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4996932042603226</v>
+        <v>0.4995552650905452</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5016852361328326</v>
+        <v>0.4943035879405016</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4981378212080046</v>
+        <v>0.490957373942625</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5088751964444038</v>
+        <v>0.5124007313629912</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5053620284858655</v>
+        <v>0.5124007313629912</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4968868556338162</v>
+        <v>0.5173146953732348</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5006354714855953</v>
+        <v>0.5391828103060536</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5038485028367904</v>
+        <v>0.4954931943667545</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5172476283975844</v>
+        <v>0.4734823837410624</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5172476283975844</v>
+        <v>0.4555364977530185</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5178050929044091</v>
+        <v>0.4623697188324067</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5143099997336347</v>
+        <v>0.4579328340886692</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5176038919774579</v>
+        <v>0.4728535713878013</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5197005673580749</v>
+        <v>0.4728797322648279</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5174207658382706</v>
+        <v>0.4787954200390416</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5185575748581605</v>
+        <v>0.4787954200390416</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.517841242479937</v>
+        <v>0.4790732009878347</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5277552635684578</v>
+        <v>0.4996356503308637</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5277552635684578</v>
+        <v>0.4989716397066937</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.523658470226068</v>
+        <v>0.5004566262171942</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5340129453532575</v>
+        <v>0.4984141751998691</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5469269055582826</v>
+        <v>0.4956715639828461</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5463152166881662</v>
+        <v>0.4968183617012371</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5450476032831425</v>
+        <v>0.5019634927339353</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5053943728429168</v>
+        <v>0.4905283355593861</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5026579451059183</v>
+        <v>0.4970276487174511</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.502020095358775</v>
+        <v>0.4996132946723136</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5110988709916779</v>
+        <v>0.4906971921292861</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5140345970463894</v>
+        <v>0.4963574546132566</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5172761675361591</v>
+        <v>0.4952487090796318</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5122437661008307</v>
+        <v>0.496323207646967</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4982771873347108</v>
+        <v>0.4982847977716641</v>
       </c>
     </row>
   </sheetData>
